--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.41713482658004</v>
+        <v>5.105284409319257</v>
       </c>
       <c r="D2" t="n">
-        <v>31.17235584142543</v>
+        <v>5.065507824231632</v>
       </c>
       <c r="E2" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F2" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.69981758386412</v>
+        <v>4.01372035737792</v>
       </c>
       <c r="D3" t="n">
-        <v>24.94938414490606</v>
+        <v>4.054274923547234</v>
       </c>
       <c r="E3" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F3" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.11652468170077</v>
+        <v>2.781435260776375</v>
       </c>
       <c r="D4" t="n">
-        <v>17.35496247263196</v>
+        <v>2.820181401802694</v>
       </c>
       <c r="E4" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F4" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.901342899791644</v>
+        <v>1.446468221216142</v>
       </c>
       <c r="D5" t="n">
-        <v>8.941605531272254</v>
+        <v>1.453010898831741</v>
       </c>
       <c r="E5" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F5" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.39949584295321</v>
+        <v>10.1399180744799</v>
       </c>
       <c r="D6" t="n">
-        <v>62.18144772940485</v>
+        <v>10.10448525602829</v>
       </c>
       <c r="E6" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F6" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.39823542616025</v>
+        <v>6.402213256751041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28000854237852</v>
+        <v>6.383001388136511</v>
       </c>
       <c r="E7" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F7" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.61762045079923</v>
+        <v>7.900363323254875</v>
       </c>
       <c r="D8" t="n">
-        <v>48.49336854160127</v>
+        <v>7.880172388010207</v>
       </c>
       <c r="E8" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F8" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.59453146693535</v>
+        <v>9.196611363376995</v>
       </c>
       <c r="D9" t="n">
-        <v>55.86947565820972</v>
+        <v>9.078789794459079</v>
       </c>
       <c r="E9" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F9" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.84429850328272</v>
+        <v>7.774698506783443</v>
       </c>
       <c r="D10" t="n">
-        <v>47.35292753707068</v>
+        <v>7.694850724773985</v>
       </c>
       <c r="E10" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F10" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62.29766661440606</v>
+        <v>10.12337082484099</v>
       </c>
       <c r="D11" t="n">
-        <v>61.88843359697739</v>
+        <v>10.05687045950883</v>
       </c>
       <c r="E11" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F11" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.02768484743155</v>
+        <v>8.616998787707628</v>
       </c>
       <c r="D12" t="n">
-        <v>52.71392206102046</v>
+        <v>8.566012334915825</v>
       </c>
       <c r="E12" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F12" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.21776083225493</v>
+        <v>7.672886135241427</v>
       </c>
       <c r="D13" t="n">
-        <v>47.74093016477299</v>
+        <v>7.757901151775611</v>
       </c>
       <c r="E13" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F13" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>54.32174710049595</v>
+        <v>8.827283903830592</v>
       </c>
       <c r="D14" t="n">
-        <v>54.80197885867747</v>
+        <v>8.90532156453509</v>
       </c>
       <c r="E14" t="n">
-        <v>16.51984867392504</v>
+        <v>2.68447540951282</v>
       </c>
       <c r="F14" t="n">
-        <v>16.3842267148187</v>
+        <v>2.662436841158039</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
